--- a/Governors_CB.xlsx
+++ b/Governors_CB.xlsx
@@ -496,20 +496,20 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>55.7</v>
+        <v>55.8</v>
       </c>
       <c r="E2" t="n">
-        <v>37.5</v>
+        <v>40.2</v>
       </c>
       <c r="F2" t="n">
-        <v>6.8</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>53.5</v>
+        <v>54.2</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>Octubre 2026</t>
         </is>
       </c>
     </row>
@@ -528,20 +528,20 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>55.1</v>
+        <v>53.7</v>
       </c>
       <c r="E3" t="n">
-        <v>39.2</v>
+        <v>40.6</v>
       </c>
       <c r="F3" t="n">
         <v>5.7</v>
       </c>
       <c r="G3" t="n">
-        <v>54.8</v>
+        <v>53.5</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>Octubre 2026</t>
         </is>
       </c>
     </row>
@@ -551,29 +551,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hugo Passalacqua</t>
+          <t>Gustavo Sáenz</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Misiones</t>
+          <t>Salta</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>53.4</v>
       </c>
       <c r="E4" t="n">
-        <v>43.2</v>
+        <v>42.7</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="G4" t="n">
-        <v>52.6</v>
+        <v>53</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>Octubre 2026</t>
         </is>
       </c>
     </row>
@@ -583,29 +583,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gustavo Sáenz</t>
+          <t>Ignacio Torres</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Chubut</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>52.9</v>
+        <v>53</v>
       </c>
       <c r="E5" t="n">
-        <v>45.2</v>
+        <v>45</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>55.3</v>
+        <v>52.7</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>Octubre 2026</t>
         </is>
       </c>
     </row>
@@ -615,29 +615,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Marcelo Orrego</t>
+          <t>Hugo Passalacqua</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Juan</t>
+          <t>Misiones</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>52.5</v>
+        <v>52.8</v>
       </c>
       <c r="E6" t="n">
-        <v>44.5</v>
+        <v>43</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="G6" t="n">
-        <v>52</v>
+        <v>55.1</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>Octubre 2026</t>
         </is>
       </c>
     </row>
@@ -656,20 +656,20 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>52.2</v>
+        <v>52.5</v>
       </c>
       <c r="E7" t="n">
-        <v>43.7</v>
+        <v>43.4</v>
       </c>
       <c r="F7" t="n">
         <v>4.1</v>
       </c>
       <c r="G7" t="n">
-        <v>51.7</v>
+        <v>52</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>Octubre 2026</t>
         </is>
       </c>
     </row>
@@ -679,29 +679,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Martín Llaryora</t>
+          <t>Marcelo Orrego</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>San Juan</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>52</v>
+        <v>51.7</v>
       </c>
       <c r="E8" t="n">
-        <v>44.2</v>
+        <v>46.3</v>
       </c>
       <c r="F8" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>52.4</v>
+        <v>52.8</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>Octubre 2026</t>
         </is>
       </c>
     </row>
@@ -711,29 +711,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ignacio Torres</t>
+          <t>Martín Llaryora</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chubut</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>51.5</v>
+        <v>51.3</v>
       </c>
       <c r="E9" t="n">
-        <v>47.1</v>
+        <v>44.6</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4</v>
+        <v>4.1</v>
       </c>
       <c r="G9" t="n">
-        <v>52.7</v>
+        <v>52.5</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>Octubre 2026</t>
         </is>
       </c>
     </row>
@@ -752,20 +752,20 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>51.4</v>
+        <v>51</v>
       </c>
       <c r="E10" t="n">
-        <v>46.6</v>
+        <v>46.2</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="G10" t="n">
-        <v>53</v>
+        <v>49.6</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>Octubre 2026</t>
         </is>
       </c>
     </row>
@@ -775,29 +775,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Juan Pablo Valdés</t>
+          <t>Raúl Jalil</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Corrientes</t>
+          <t>Catamarca</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>51</v>
+        <v>50.8</v>
       </c>
       <c r="E11" t="n">
-        <v>43.1</v>
+        <v>44.9</v>
       </c>
       <c r="F11" t="n">
-        <v>5.9</v>
+        <v>4.3</v>
       </c>
       <c r="G11" t="n">
-        <v>51.1</v>
+        <v>48.8</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>Octubre 2026</t>
         </is>
       </c>
     </row>
@@ -807,29 +807,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Carlos Sadir</t>
+          <t>Juan Pablo Valdés</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jujuy</t>
+          <t>Corrientes</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>50.7</v>
+        <v>50.4</v>
       </c>
       <c r="E12" t="n">
-        <v>44.3</v>
+        <v>47.1</v>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G12" t="n">
-        <v>49.5</v>
+        <v>51.9</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>Octubre 2026</t>
         </is>
       </c>
     </row>
@@ -839,29 +839,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Raúl Jalil</t>
+          <t>Leandro Zdero</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Catamarca</t>
+          <t>Chaco</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>50.4</v>
+        <v>50.1</v>
       </c>
       <c r="E13" t="n">
-        <v>46.8</v>
+        <v>46.1</v>
       </c>
       <c r="F13" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="G13" t="n">
-        <v>50.2</v>
+        <v>51.1</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>Octubre 2026</t>
         </is>
       </c>
     </row>
@@ -880,20 +880,20 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>50.2</v>
+        <v>49.6</v>
       </c>
       <c r="E14" t="n">
-        <v>36.4</v>
+        <v>43</v>
       </c>
       <c r="F14" t="n">
-        <v>13.4</v>
+        <v>7.4</v>
       </c>
       <c r="G14" t="n">
-        <v>50</v>
+        <v>49.1</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>Octubre 2026</t>
         </is>
       </c>
     </row>
@@ -912,20 +912,20 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>49.5</v>
+        <v>49.2</v>
       </c>
       <c r="E15" t="n">
-        <v>46.2</v>
+        <v>47.1</v>
       </c>
       <c r="F15" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="G15" t="n">
-        <v>49</v>
+        <v>48.4</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>Octubre 2026</t>
         </is>
       </c>
     </row>
@@ -935,29 +935,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Leandro Zdero</t>
+          <t>Claudio Vidal</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chaco</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="E16" t="n">
-        <v>47.1</v>
+        <v>48.5</v>
       </c>
       <c r="F16" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="G16" t="n">
-        <v>47.2</v>
+        <v>48.2</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>Octubre 2026</t>
         </is>
       </c>
     </row>
@@ -967,29 +967,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sergio Ziliotto</t>
+          <t>Carlos Sadir</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>La Pampa</t>
+          <t>Jujuy</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>47.3</v>
+        <v>48.5</v>
       </c>
       <c r="E17" t="n">
-        <v>50.1</v>
+        <v>45.9</v>
       </c>
       <c r="F17" t="n">
-        <v>2.6</v>
+        <v>5.6</v>
       </c>
       <c r="G17" t="n">
-        <v>47.7</v>
+        <v>50.3</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>Octubre 2026</t>
         </is>
       </c>
     </row>
@@ -999,29 +999,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Claudio Vidal</t>
+          <t>Sergio Ziliotto</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>La Pampa</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>47</v>
+        <v>48.3</v>
       </c>
       <c r="E18" t="n">
         <v>49.5</v>
       </c>
       <c r="F18" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="G18" t="n">
-        <v>46.8</v>
+        <v>47.6</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>Octubre 2026</t>
         </is>
       </c>
     </row>
@@ -1040,20 +1040,20 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>46.8</v>
+        <v>47.1</v>
       </c>
       <c r="E19" t="n">
-        <v>49.3</v>
+        <v>49</v>
       </c>
       <c r="F19" t="n">
         <v>3.9</v>
       </c>
       <c r="G19" t="n">
-        <v>46.4</v>
+        <v>47.3</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>Octubre 2026</t>
         </is>
       </c>
     </row>
@@ -1063,29 +1063,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Alberto Weretilneck</t>
+          <t>Alfredo Cornejo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Río Negro</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>46.5</v>
+        <v>45.2</v>
       </c>
       <c r="E20" t="n">
-        <v>50.8</v>
+        <v>52.3</v>
       </c>
       <c r="F20" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="G20" t="n">
-        <v>46</v>
+        <v>45.9</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>Octubre 2026</t>
         </is>
       </c>
     </row>
@@ -1095,29 +1095,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Gustavo Melella</t>
+          <t>Alberto Weretilneck</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tierra del Fuego</t>
+          <t>Río Negro</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>45.2</v>
+        <v>44.9</v>
       </c>
       <c r="E21" t="n">
-        <v>51.4</v>
+        <v>51.6</v>
       </c>
       <c r="F21" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G21" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>Octubre 2026</t>
         </is>
       </c>
     </row>
@@ -1127,29 +1127,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Alfredo Cornejo</t>
+          <t>Gildo Insfrán</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Formosa</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>45.1</v>
+        <v>44</v>
       </c>
       <c r="E22" t="n">
-        <v>50.1</v>
+        <v>51.7</v>
       </c>
       <c r="F22" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="G22" t="n">
-        <v>45.3</v>
+        <v>42.8</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>Octubre 2026</t>
         </is>
       </c>
     </row>
@@ -1159,29 +1159,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Axel Kicillof</t>
+          <t>Gustavo Melella</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Tierra del Fuego</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>44.2</v>
+        <v>43.5</v>
       </c>
       <c r="E23" t="n">
-        <v>53.3</v>
+        <v>52.5</v>
       </c>
       <c r="F23" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>43.9</v>
+        <v>44</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>Octubre 2026</t>
         </is>
       </c>
     </row>
@@ -1191,29 +1191,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ricardo Quintela</t>
+          <t>Axel Kicillof</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>La Rioja</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>42.6</v>
+        <v>43.1</v>
       </c>
       <c r="E24" t="n">
-        <v>55.2</v>
+        <v>54.4</v>
       </c>
       <c r="F24" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="G24" t="n">
-        <v>43</v>
+        <v>43.4</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>Octubre 2026</t>
         </is>
       </c>
     </row>
@@ -1223,29 +1223,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Gildo Insfrán</t>
+          <t>Ricardo Quintela</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Formosa</t>
+          <t>La Rioja</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>40.7</v>
+        <v>42.8</v>
       </c>
       <c r="E25" t="n">
-        <v>55</v>
+        <v>54.1</v>
       </c>
       <c r="F25" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="G25" t="n">
-        <v>43.6</v>
+        <v>42.3</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>Octubre 2026</t>
         </is>
       </c>
     </row>
